--- a/example.xlsx
+++ b/example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tmd\android\_RTP_RESPIN_ADJUST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A81148-13EB-4D59-953E-9F31ED958130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB4D54A-D631-4D48-8433-596C65230ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="3240" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="2385" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -80,12 +80,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -102,12 +96,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -409,10 +400,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4">
+      <c r="A2" s="3">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
         <v>1E-3</v>
       </c>
       <c r="C2" s="1">
@@ -421,15 +412,15 @@
       <c r="D2" s="1">
         <v>0.67960259999999995</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>1E-3</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
       <c r="C3" s="1">
@@ -438,15 +429,15 @@
       <c r="D3" s="1">
         <v>0.14897299999999999</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
       <c r="C4" s="1">
@@ -455,15 +446,15 @@
       <c r="D4" s="1">
         <v>4.6072200000000001E-2</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
       <c r="C5" s="1">
@@ -472,15 +463,15 @@
       <c r="D5" s="1">
         <v>2.31156E-2</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>3</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
       <c r="C6" s="1">
@@ -489,15 +480,15 @@
       <c r="D6" s="1">
         <v>1.3857400000000001E-2</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
       <c r="C7" s="1">
@@ -506,15 +497,15 @@
       <c r="D7" s="1">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>5</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>10</v>
       </c>
       <c r="C8" s="1">
@@ -523,15 +514,15 @@
       <c r="D8" s="1">
         <v>3.1554600000000002E-2</v>
       </c>
-      <c r="E8" s="2">
-        <v>0.28999999999999998</v>
+      <c r="E8" s="3">
+        <v>2900</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>10</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>15</v>
       </c>
       <c r="C9" s="1">
@@ -540,15 +531,15 @@
       <c r="D9" s="1">
         <v>1.26558E-2</v>
       </c>
-      <c r="E9" s="2">
-        <v>0.4</v>
+      <c r="E9" s="3">
+        <v>4000</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>15</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>20</v>
       </c>
       <c r="C10" s="1">
@@ -557,15 +548,15 @@
       <c r="D10" s="1">
         <v>6.1244000000000003E-3</v>
       </c>
-      <c r="E10" s="2">
-        <v>0.4</v>
+      <c r="E10" s="3">
+        <v>4000</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>20</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>25</v>
       </c>
       <c r="C11" s="1">
@@ -574,15 +565,15 @@
       <c r="D11" s="1">
         <v>4.7505999999999998E-3</v>
       </c>
-      <c r="E11" s="2">
-        <v>0.8</v>
+      <c r="E11" s="3">
+        <v>8000</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>25</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>50</v>
       </c>
       <c r="C12" s="1">
@@ -591,15 +582,15 @@
       <c r="D12" s="1">
         <v>9.8960000000000003E-3</v>
       </c>
-      <c r="E12" s="2">
-        <v>0.96</v>
+      <c r="E12" s="3">
+        <v>9600</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>50</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>75</v>
       </c>
       <c r="C13" s="1">
@@ -608,15 +599,15 @@
       <c r="D13" s="1">
         <v>5.8809999999999999E-3</v>
       </c>
-      <c r="E13" s="2">
-        <v>0.98499999999999999</v>
+      <c r="E13" s="3">
+        <v>9850</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>75</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>100</v>
       </c>
       <c r="C14" s="1">
@@ -625,15 +616,15 @@
       <c r="D14" s="1">
         <v>3.0508000000000002E-3</v>
       </c>
-      <c r="E14" s="2">
-        <v>0.997</v>
+      <c r="E14" s="3">
+        <v>9970</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>100</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>150</v>
       </c>
       <c r="C15" s="1">
@@ -642,15 +633,15 @@
       <c r="D15" s="1">
         <v>3.8847999999999999E-3</v>
       </c>
-      <c r="E15" s="2">
-        <v>0.998</v>
+      <c r="E15" s="3">
+        <v>9980</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>150</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>250</v>
       </c>
       <c r="C16" s="1">
@@ -659,15 +650,15 @@
       <c r="D16" s="1">
         <v>2.8379999999999998E-3</v>
       </c>
-      <c r="E16" s="2">
-        <v>0.99950000000000006</v>
+      <c r="E16" s="3">
+        <v>9995</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>250</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>500</v>
       </c>
       <c r="C17" s="1">
@@ -676,15 +667,15 @@
       <c r="D17" s="1">
         <v>3.0404E-3</v>
       </c>
-      <c r="E17" s="2">
-        <v>1</v>
+      <c r="E17" s="3">
+        <v>10000</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>500</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>1000</v>
       </c>
       <c r="C18" s="1">
@@ -693,25 +684,25 @@
       <c r="D18" s="1">
         <v>2.028E-4</v>
       </c>
-      <c r="E18" s="2">
-        <v>1</v>
+      <c r="E18" s="3">
+        <v>10000</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>1000</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="3">
         <v>9999999</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <v>0</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
-      <c r="E19" s="2">
-        <v>0</v>
+      <c r="E19" s="3">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
